--- a/data/trans_bre/P1417-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1417-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>171,79%</t>
+          <t>141,62%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,38</t>
+          <t>0,35; 2,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,84</t>
+          <t>1,38; 3,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,76</t>
+          <t>0,8; 4,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,61</t>
+          <t>0,99; 3,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,6; —</t>
+          <t>-40,1; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,31; 1134,6</t>
+          <t>36,05; 1163,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,02; 374,27</t>
+          <t>37,02; 365,61</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>242,28%</t>
+          <t>178,6%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,92</t>
+          <t>0,27; 1,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,06</t>
+          <t>1,42; 3,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,38</t>
+          <t>0,28; 2,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,41</t>
+          <t>1,54; 3,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1767,42</t>
+          <t>11,33; 1597,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>103,62; 1044,61</t>
+          <t>101,31; 1080,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 544,36</t>
+          <t>14,19; 556,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>108,34; 687,07</t>
+          <t>62,29; 359,01</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>321,16%</t>
+          <t>443,29%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,83</t>
+          <t>1,13; 3,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,09</t>
+          <t>1,55; 4,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,84</t>
+          <t>0,53; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,75</t>
+          <t>3,15; 6,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,87; —</t>
+          <t>34,43; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,82; 905,88</t>
+          <t>16,82; 1012,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,41; 929,84</t>
+          <t>167,42; 1060,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>394,49%</t>
+          <t>403,23%</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,86</t>
+          <t>0,07; 1,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,88</t>
+          <t>0,76; 2,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,85</t>
+          <t>1,7; 3,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,65</t>
+          <t>2,42; 4,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 875,41</t>
+          <t>-2,11; 656,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,58; 839,48</t>
+          <t>47,67; 923,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>150,77; 818,32</t>
+          <t>167,25; 901,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>273,35%</t>
+          <t>264,28%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,83</t>
+          <t>0,8; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,97</t>
+          <t>1,71; 2,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,51</t>
+          <t>1,32; 2,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,86</t>
+          <t>2,6; 3,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>119,47; 735,4</t>
+          <t>125,2; 667,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>268,3; 1093,33</t>
+          <t>267,68; 970,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>168,04; 658,49</t>
+          <t>167,1; 647,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>157,51; 425,18</t>
+          <t>164,03; 383,6</t>
         </is>
       </c>
     </row>
